--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136902420</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136902437</v>
       </c>
       <c r="B5" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136902420</v>
       </c>
       <c r="B4" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136902437</v>
       </c>
       <c r="B5" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -941,11 +941,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1055,11 +1051,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136902420</v>
       </c>
       <c r="B4" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902437</v>
       </c>
       <c r="B5" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136902420</v>
       </c>
       <c r="B4" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902437</v>
       </c>
       <c r="B5" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136902420</v>
       </c>
       <c r="B4" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902437</v>
       </c>
       <c r="B5" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136902046</v>
       </c>
       <c r="B3" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37887-2026 artfynd.xlsx
+++ b/artfynd/A 37887-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902094</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136902316</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
